--- a/config/replace.xlsx
+++ b/config/replace.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\NLP\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3B2E55-67F7-4BA9-8626-87888FADD923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE034B8A-A1EA-4777-992B-CD445AC46B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-10790" windowWidth="21820" windowHeight="38620" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="报告" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5957" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6395" uniqueCount="1220">
   <si>
     <t>原始值</t>
   </si>
@@ -4971,6 +4971,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -5034,7 +5035,27 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10805,7 +10826,7 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10814,7 +10835,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F097E3-1F48-421A-B558-96337FA1212F}">
-  <dimension ref="A1:C600"/>
+  <dimension ref="A1:C701"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="36.125" customWidth="1"/>
@@ -17289,15 +17310,1114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A601" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C601" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A602" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C602" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A603" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C603" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A604" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C604" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A605" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C605" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A606" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A607" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A608" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B608" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="C608" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A609" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B609" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C609" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A610" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B610" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C610" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A611" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B611" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C611" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A612" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C612" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A613" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C613" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A614" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C614" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A615" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C615" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A616" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="C616" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A617" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C617" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A618" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C618" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A619" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C619" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A620" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="C620" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A621" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="C621" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A622" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C622" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A623" t="s">
+        <v>816</v>
+      </c>
+      <c r="B623" t="s">
+        <v>817</v>
+      </c>
+      <c r="C623" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A624" t="s">
+        <v>840</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="C624" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A625" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B625" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="C625" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A626" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="B626" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="C626" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A627" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C627" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A628" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C628" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A629" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C629" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A630" t="s">
+        <v>871</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="C630" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A631" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C631" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A632" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C632" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A633" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C633" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A634" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C634" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A635" t="s">
+        <v>911</v>
+      </c>
+      <c r="B635" t="s">
+        <v>910</v>
+      </c>
+      <c r="C635" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A636" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B636" t="s">
+        <v>910</v>
+      </c>
+      <c r="C636" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A637" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C637" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A638" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="C638" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A639" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="C639" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A640" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C640" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A641" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="C641" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A642" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C642" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A643" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C643" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A644" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C644" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A645" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C645" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A646" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C646" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A647" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C647" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A648" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C648" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A649" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C649" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A650" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C650" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A651" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C651" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A652" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C652" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A653" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C653" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A654" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C654" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A655" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C655" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A656" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C656" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A657" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C657" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A658" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C658" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A659" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C659" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A660" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C660" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A661" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C661" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A662" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C662" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A663" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C663" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A664" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C664" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A665" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C665" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A666" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C666" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A667" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C667" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A668" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C668" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A669" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C669" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A670" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C670" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A671" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C671" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A672" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C672" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A673" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C673" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A674" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C674" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A675" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B675" t="s">
+        <v>959</v>
+      </c>
+      <c r="C675" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A676" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C676" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A677" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C677" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A678" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C678" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A679" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C679" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A680" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C680" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A681" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C681" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A682" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C682" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A683" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C683" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A684" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C684" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A685" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C685" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A686" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C686" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A687" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C687" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A688" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B688" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C688" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A689" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C689" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A690" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C690" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A691" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C691" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A692" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C692" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A693" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C693" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A694" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B694" t="s">
+        <v>37</v>
+      </c>
+      <c r="C694" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A695" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C695" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A696" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C696" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A697" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C697" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A698" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C698" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A699" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C699" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A700" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C700" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A701" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C701" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="B626">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1334AE-C33B-4AC8-A780-41B8CB23E2EC}">
-  <dimension ref="A1:C600"/>
+  <dimension ref="A1:C701"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -23772,16 +24892,1118 @@
         <v>0</v>
       </c>
     </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A601" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C601" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A602" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C602" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A603" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C603" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A604" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C604" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A605" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C605" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A606" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A607" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A608" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B608" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="C608" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A609" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B609" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C609" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A610" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B610" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C610" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A611" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B611" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C611" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A612" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C612" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A613" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="C613" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A614" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="C614" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A615" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C615" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A616" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="C616" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A617" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C617" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A618" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="C618" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A619" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="C619" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A620" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="C620" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A621" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="C621" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A622" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C622" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A623" t="s">
+        <v>816</v>
+      </c>
+      <c r="B623" t="s">
+        <v>817</v>
+      </c>
+      <c r="C623" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A624" t="s">
+        <v>840</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="C624" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A625" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B625" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="C625" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A626" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="B626" s="7" t="s">
+        <v>843</v>
+      </c>
+      <c r="C626" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A627" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="C627" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A628" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="C628" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A629" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="C629" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A630" t="s">
+        <v>871</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="C630" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A631" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C631" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A632" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C632" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A633" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C633" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A634" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C634" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A635" t="s">
+        <v>911</v>
+      </c>
+      <c r="B635" t="s">
+        <v>910</v>
+      </c>
+      <c r="C635" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A636" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B636" t="s">
+        <v>910</v>
+      </c>
+      <c r="C636" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A637" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C637" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A638" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B638" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="C638" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A639" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B639" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="C639" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A640" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C640" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A641" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="C641" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A642" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C642" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A643" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C643" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A644" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C644" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A645" s="8" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C645" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A646" s="8" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C646" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A647" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C647" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A648" s="8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C648" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A649" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C649" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A650" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C650" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A651" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C651" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" ht="15" x14ac:dyDescent="0.15">
+      <c r="A652" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C652" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A653" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C653" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A654" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C654" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A655" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C655" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A656" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C656" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A657" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C657" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A658" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C658" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A659" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C659" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A660" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C660" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A661" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C661" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A662" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C662" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A663" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C663" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A664" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C664" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A665" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C665" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A666" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C666" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A667" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C667" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A668" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C668" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A669" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C669" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A670" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C670" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A671" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C671" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A672" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B672" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C672" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A673" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B673" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C673" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A674" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B674" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C674" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A675" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B675" t="s">
+        <v>959</v>
+      </c>
+      <c r="C675" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A676" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B676" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C676" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A677" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B677" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C677" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A678" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C678" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A679" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B679" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C679" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A680" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B680" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C680" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A681" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C681" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A682" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B682" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C682" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A683" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B683" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C683" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A684" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C684" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A685" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B685" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C685" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A686" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B686" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C686" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A687" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B687" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C687" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A688" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B688" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C688" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A689" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B689" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C689" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A690" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C690" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A691" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C691" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A692" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C692" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A693" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C693" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A694" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B694" t="s">
+        <v>37</v>
+      </c>
+      <c r="C694" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A695" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C695" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A696" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C696" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A697" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C697" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A698" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C698" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A699" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C699" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A700" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C700" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A701" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C701" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="B626">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354AF659-B9B7-403D-A334-F7FFBE35C4F1}">
-  <dimension ref="A1:C594"/>
+  <dimension ref="A1:C616"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="3" width="21.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
@@ -30183,6 +32405,242 @@
       </c>
       <c r="C594" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A595" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C595" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A596" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C596" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A597" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="C597" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A598" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C598" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A599" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C599" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A600" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C600" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A601" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C601" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A602" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B602" s="8" t="s">
+        <v>882</v>
+      </c>
+      <c r="C602" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A603" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B603" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C603" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A604" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B604" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C604" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A605" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B605" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C605" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A606" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C606" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A607" s="10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C607" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A608" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C608" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A609" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C609" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A610" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C610" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A611" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B611" t="s">
+        <v>37</v>
+      </c>
+      <c r="C611" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A612" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C612" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A613" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C613" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A614" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C614" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A615" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C615" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A616" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C616" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -30193,8 +32651,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1D13F9-6BC3-4B12-9A34-D34B69020D46}">
-  <dimension ref="A1:C594"/>
+  <dimension ref="A1:C595"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="3" width="25.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
@@ -36596,6 +39057,17 @@
       </c>
       <c r="C594" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A595" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="C595" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
